--- a/AAII_Financials/Quarterly/FNMA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FNMA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>FNMA</t>
   </si>
@@ -656,271 +656,277 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7054000</v>
+      </c>
+      <c r="E8" s="3">
         <v>6857000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6888000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6990000</v>
       </c>
-      <c r="G8" s="3">
-        <v>6475000</v>
-      </c>
       <c r="H8" s="3">
+        <v>6464000</v>
+      </c>
+      <c r="I8" s="3">
         <v>7174000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7773000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7413000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8024000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7785000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7530000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8763000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8798000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6846000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>32642000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>30938000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>29531000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>27422000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>26085000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>25092000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>25209000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>23646000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>24951000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>26127000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>27327000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>29444000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>29503000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>29818000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>30280000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>30646000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>30346000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>29501000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>28986000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>28727000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5619000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>6540000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5412000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5639000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>6261000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>5666000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -963,208 +969,214 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>26361000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>24559000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>22483000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20764000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19239000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18790000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>17578000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>17548000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>18403000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>20057000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>22120000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>24614000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>24076000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>24895000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>25540000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>26309000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>25810000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>24437000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>23935000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>23732000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>621000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>603000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>575000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>547000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>529000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>521000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>7054000</v>
+      </c>
+      <c r="E10" s="3">
         <v>6857000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6888000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6990000</v>
       </c>
-      <c r="G10" s="3">
-        <v>6475000</v>
-      </c>
       <c r="H10" s="3">
+        <v>6464000</v>
+      </c>
+      <c r="I10" s="3">
         <v>7174000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7773000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7413000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8024000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7785000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>7530000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8763000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8798000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6846000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6281000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6379000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>7048000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6658000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>6846000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>6302000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>7631000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6098000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6548000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>6070000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>5207000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>4830000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>5427000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>4923000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>4740000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>4337000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>4536000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>5064000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>5051000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>4995000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>4998000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>5937000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>4837000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>5092000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>5732000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>5145000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1507,33 +1526,33 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
         <v>162000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>256000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>233000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>181000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-283000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>488000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>264000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-2587000</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1546,8 +1565,8 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1564,8 +1583,8 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
-      <c r="AN14" s="3" t="s">
-        <v>8</v>
+      <c r="AN14" s="3">
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>8</v>
@@ -1573,8 +1592,11 @@
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1707000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1825000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2112000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1737000</v>
       </c>
-      <c r="G17" s="3">
-        <v>1944000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1933000</v>
+      </c>
+      <c r="I17" s="3">
         <v>2120000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2165000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1968000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2012000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1925000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2186000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2292000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1977000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1853000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>30722000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>28073000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23656000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21849000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>19593000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18984000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16175000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>17331000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>19242000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>20749000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>24113000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>28866000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>24273000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>24819000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>25959000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>27619000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>26288000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>24445000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>23393000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>23335000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>663000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1992000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>625000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1483000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>-1319000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>943000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5347000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5032000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4776000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5253000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4531000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5054000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5608000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5445000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6012000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5860000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5344000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>6471000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6821000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4993000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1920000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2865000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>5875000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>5573000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6492000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6108000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>9034000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6315000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5709000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5378000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3214000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>578000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>5230000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4999000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4321000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>3027000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4058000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>5056000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>5593000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>5392000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>4956000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>4548000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>4787000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>4156000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>7580000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>4723000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,53 +2056,54 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>358000</v>
+      </c>
+      <c r="E20" s="3">
         <v>368000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>366000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>418000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>377000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>470000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>429000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>392000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>408000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>427000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>388000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>530000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>542000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>213000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2146,53 +2179,56 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4989000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4664000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4410000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4835000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4154000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4584000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5179000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5053000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5604000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5433000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4956000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5941000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6279000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4780000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2268,8 +2304,11 @@
       <c r="AP21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,8 +2351,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4989000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4664000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4410000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4835000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4154000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4584000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5179000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5053000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5604000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5433000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4956000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5941000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6279000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4780000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1920000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2865000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5875000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5573000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6492000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6108000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9034000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6315000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5709000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5378000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3214000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>578000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5230000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4999000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4321000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3027000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4058000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5056000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5593000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5392000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>4956000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>4548000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>4787000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>4156000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>7580000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>4723000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1007000</v>
+      </c>
+      <c r="E24" s="3">
         <v>944000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>883000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>976000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>837000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>923000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1049000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1009000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1120000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1113000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1013000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1242000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1285000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1008000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>494000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>429000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1222000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1165000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1303000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1266000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1882000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1322000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1139000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1149000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>669000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>117000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>865000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1036000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>889000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>627000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>828000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1045000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1136000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1131000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1589000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1525000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1587000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1383000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>2545000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>1527000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3982000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3720000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3527000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3859000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3317000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3661000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4130000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4044000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4484000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4320000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3943000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4699000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4994000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3772000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1426000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2436000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4653000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4408000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5189000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4842000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7152000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4993000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4570000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4229000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2545000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>461000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4365000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3963000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3432000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2400000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3230000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4011000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4457000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4261000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3367000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>3023000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>3200000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>2773000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>5035000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>3196000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>152000</v>
+      </c>
+      <c r="E27" s="3">
         <v>65000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10828000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3859000</v>
       </c>
-      <c r="G27" s="3">
-        <v>6972000</v>
-      </c>
       <c r="H27" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="I27" s="3">
         <v>6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12845000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4044000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8808000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-4000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>-11000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>14000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>32000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>27000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4000</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>13000</v>
       </c>
       <c r="AA27" s="3">
         <v>13000</v>
       </c>
       <c r="AB27" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>99000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>67000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>39000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>36000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3323000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3367000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-25000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>83000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-436000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>219000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-9900000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,53 +3554,56 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-358000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-368000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-366000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-418000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-377000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-470000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-429000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-392000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-408000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-427000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-388000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-530000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-542000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-213000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3610,130 +3679,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3982000</v>
+      </c>
+      <c r="E33" s="3">
         <v>3720000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3527000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3859000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3317000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3661000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4130000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4044000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4484000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4320000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3943000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4699000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4994000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3772000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-11000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>14000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>32000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>27000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4000</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>13000</v>
       </c>
       <c r="AA33" s="3">
         <v>13000</v>
       </c>
       <c r="AB33" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>99000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>67000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>39000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>36000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3323000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-6533000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-25000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>83000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-436000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>219000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3982000</v>
+      </c>
+      <c r="E35" s="3">
         <v>3720000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3527000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3859000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3317000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3661000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4130000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4044000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4484000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4320000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3943000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4699000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4994000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3772000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-11000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>14000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>32000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>27000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4000</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>13000</v>
       </c>
       <c r="AA35" s="3">
         <v>13000</v>
       </c>
       <c r="AB35" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>99000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>67000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>39000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>36000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3323000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-6533000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-25000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>83000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-436000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>219000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,175 +4276,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11413000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11485000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11452000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12155000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>38229000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>39352000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13477000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38146000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41911000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12524000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>35817000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>48604000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52229000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>60330000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>57987000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>35640000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41639000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>36330000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>42448000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>67377000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>48879000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26538000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>38337000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>37472000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>54510000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>80463000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>21184000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>22592000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>30791000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>27496000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>25557000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>27789000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>20853000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>10248000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>32110000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>23914000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>16904000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>24988000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>25224000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>26559000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>84469000</v>
+      </c>
+      <c r="E42" s="3">
         <v>92195000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>107141000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>123269000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>91045000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>101398000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>126257000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>18345000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27869000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>73827000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>77754000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>22999000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>33195000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>27103000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4435,53 +4524,56 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4132672000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4130525000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4134509000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4137710000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4133627000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4139914000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4150891000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4151317000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4141641000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4140378000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4145902000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4145196000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4134079000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4122402000</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4557,8 +4649,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4601,8 +4696,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4679,52 +4774,55 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9300000</v>
+      </c>
+      <c r="E45" s="3">
         <v>9100000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8200000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9500000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9700000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9400000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8900000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>5700000</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4801,53 +4899,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4267903000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4277283000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4292642000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4310662000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4313317000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4329284000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4324957000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4247712000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4248469000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4249369000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4300211000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4252581000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4247222000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4240854000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4923,130 +5024,136 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>38874000</v>
+      </c>
+      <c r="E47" s="3">
         <v>12424000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>375000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>412000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>438000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>445000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>469000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>61790000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>49899000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>49896000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>564000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>51872000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>51231000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>51089000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4189647000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4197150000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4182463000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4163263000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4087292000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4039269000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4001420000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3917568000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3830268000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3714158000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3603328000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3434623000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3406871000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3393131000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3347510000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3335054000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3336119000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3307170000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3271028000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3281472000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3237517000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>3219348000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>3200317000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>3190167000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>3159093000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>3117723000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -5092,83 +5199,86 @@
       <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S48" s="3">
         <v>1539000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1485000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1456000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1259000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1261000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1138000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1183000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1261000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1462000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1844000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2224000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2366000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2452000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2398000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2489000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2584000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2722000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2816000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3044000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3220000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3581000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3696000</v>
       </c>
-      <c r="AN48" s="3">
-        <v>0</v>
-      </c>
       <c r="AO48" s="3">
         <v>0</v>
       </c>
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5289,8 +5399,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16381000</v>
+      </c>
+      <c r="E52" s="3">
         <v>15498000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14693000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14782000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14345000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13527000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13760000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14086000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14489000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13029000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12981000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>13042000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13267000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12902000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>42765000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>40650000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>46705000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>65726000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>78898000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>79215000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>88995000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>100319000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>90233000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>86324000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>78833000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>61076000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>52133000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>53900000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>42700000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>38156000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>37054000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>37610000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>43251000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>43629000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>45500000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>58591000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>62401000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>59968000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>70483000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>78027000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4332343000</v>
+      </c>
+      <c r="E54" s="3">
         <v>4314635000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4317538000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4335856000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4338227000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4353709000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4349731000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4334556000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4323893000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4323819000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4325437000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4329380000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4323710000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4317460000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4305288000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4289453000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>4288967000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4285029000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4229166000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4209209000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4158038000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4070103000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3985749000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3864603000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3760676000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3601356000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3503319000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3494436000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3443287000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3421034000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3418318000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3401105000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3363364000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3364402000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3345529000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>3330759000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>3309230000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>3303754000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>3287968000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>3255942000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,8 +6116,9 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6031,8 +6161,8 @@
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -6109,53 +6239,56 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>27667000</v>
+      </c>
+      <c r="E58" s="3">
         <v>20602000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>65725000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19922000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11095000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11198000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11342000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11551000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12089000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14363000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>17454000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14321000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15925000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14275000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6231,8 +6364,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6275,131 +6411,134 @@
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>9917000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>9650000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9355000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9270000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9186000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9299000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>9374000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>9585000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9719000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9982000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10054000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10246000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10228000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10400000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10342000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10364000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10211000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10105000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>9825000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>9773000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>9682000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>9637000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>9473000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>9588000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>9431000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>9512000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40090000</v>
+      </c>
+      <c r="E60" s="3">
         <v>32815000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>78614000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>32002000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>22936000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>23959000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>23788000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>23002000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23265000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25484000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29246000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25079000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26338000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24457000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6475,175 +6614,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4160591000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4152200000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4114856000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4183413000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4199417000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4217617000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4216909000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4206359000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4200956000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4202289000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4205404000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4217517000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4216722000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4216799000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4221888000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4207814000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4208647000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4208797000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4158191000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4142469000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4096275000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4013980000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3935736000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3819804000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3719975000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3562556000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3467386000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3461858000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3416579000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3395010000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3391920000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3374370000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3337489000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3340472000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3330054000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3308583000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3287667000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3281654000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3262316000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>3233113000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15165000</v>
+      </c>
+      <c r="E62" s="3">
         <v>16953000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>15056000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14956000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14238000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13821000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14377000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14665000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13189000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14040000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13105000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13059000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11606000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12155000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6719,8 +6864,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4215846000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4201968000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4208526000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4230371000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4236591000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4255397000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4255074000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4244026000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4237410000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4241813000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4247755000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4255655000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4254666000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>4253411000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4245011000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4230613000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4232560000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4233271000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4181809000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4167036000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4120693000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4039878000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3960490000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3843910000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3744199000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3587411000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3488711000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3484094000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3436922000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3415673000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3412078000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3394130000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3355905000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3360464000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3349215000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3327111000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>3305513000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>3300375000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>3281897000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>3251766000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7600,7 +7767,7 @@
         <v>139966000</v>
       </c>
       <c r="AK70" s="3">
-        <v>136279000</v>
+        <v>139966000</v>
       </c>
       <c r="AL70" s="3">
         <v>136279000</v>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>136279000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>136279000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-16559000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-20541000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-24261000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-27788000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-31647000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-34964000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-38625000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-42755000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-46799000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-51283000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-55603000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-59546000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-64245000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-69239000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-73011000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-74437000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-76873000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-81526000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-85934000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-91123000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-95965000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-103117000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-108110000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-112680000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-116909000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-119454000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-118776000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-123141000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-127104000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-128175000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-127335000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-126591000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-126143000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-129662000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-133805000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-126625000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-126531000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-126952000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-124253000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-126312000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-23469000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-27299000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-30954000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-34481000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-38330000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-41654000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-45309000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-49436000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-53483000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-57960000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-62284000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-66241000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-70922000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-75917000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-79689000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-81126000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-83559000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-88208000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-92609000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-97793000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-102621000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-109741000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-114707000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-119273000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-123489000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-126021000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-125358000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-129624000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-133601000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-134605000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-133726000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-132991000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-132507000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-136028000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-139965000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-132631000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>-132562000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>-132900000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>-130208000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>-132103000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3982000</v>
+      </c>
+      <c r="E81" s="3">
         <v>3720000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3527000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3859000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3317000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3661000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4130000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4044000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4484000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4320000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3943000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4699000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4994000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3772000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-11000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>14000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>32000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>27000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4000</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>13000</v>
       </c>
       <c r="AA81" s="3">
         <v>13000</v>
       </c>
       <c r="AB81" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>99000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>67000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>39000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>36000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3323000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-6533000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-25000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>83000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-436000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>219000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,8 +8961,9 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8808,8 +9006,8 @@
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8886,8 +9084,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9253000</v>
+      </c>
+      <c r="E89" s="3">
         <v>16484000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5991000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9585000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4908000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3505000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-12384000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6758000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1487000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7135000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2035000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3603000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2230000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4015000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>10415000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9248000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>20805000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3358000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10156000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-2984000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15156000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>24883000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4060000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-37672000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-41496000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2174000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-7930000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>996000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>364000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1816000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4044000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-121000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-266000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1409000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4133000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3861000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-2411000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2673000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>4016000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-767000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,8 +9881,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9706,8 +9926,8 @@
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9784,8 +10004,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>9490000</v>
+      </c>
+      <c r="E94" s="3">
         <v>32859000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>65737000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>41920000</v>
       </c>
-      <c r="G94" s="3">
-        <v>55097000</v>
-      </c>
       <c r="H94" s="3">
+        <v>54698000</v>
+      </c>
+      <c r="I94" s="3">
         <v>24699000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>40762000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>40950000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>82826000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12293000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>23907000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>35573000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>22101000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>17569000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>37665000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>21098000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>27043000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>4322000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>40559000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>52668000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>12064000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-14441000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19898000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>19855000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-20936000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>47664000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>72305000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>39241000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>48060000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>47446000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>40289000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>30058000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>64690000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>15816000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>48959000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>51181000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>49546000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>43525000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>48673000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>61443000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,8 +10471,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10316,8 +10549,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,130 +10924,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-23193000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-46662000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-68520000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-50407000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-59250000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-28669000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27764000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-39858000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-39254000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-30294000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-39035000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-36812000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-35733000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-18588000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-23800000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-42727000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-60887000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-27330000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-75548000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-41519000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-16262000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11724000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>20473000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>8581000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>53948000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>17463000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-67466000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-36709000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-39695000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-46444000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-45941000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-27635000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-53055000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-37307000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-40853000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-51920000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-51385000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-46380000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-54024000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-57736000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10848,8 +11096,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10926,126 +11174,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4450000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2681000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3208000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1098000</v>
       </c>
-      <c r="G102" s="3">
-        <v>755000</v>
-      </c>
       <c r="H102" s="3">
+        <v>356000</v>
+      </c>
+      <c r="I102" s="3">
         <v>-465000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>614000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5666000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>45059000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-35452000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13093000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2364000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-11402000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2996000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>24280000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12381000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13039000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-19650000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-24833000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8165000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>10958000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1282000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>4635000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-9236000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8484000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>67301000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3091000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3528000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>8729000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2818000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1608000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>2302000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>11369000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-22900000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>8196000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>7010000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-8084000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-236000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1335000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>2940000</v>
       </c>
     </row>
